--- a/reports/phase3_5/parser_qa.xlsx
+++ b/reports/phase3_5/parser_qa.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parser_qa" sheetId="1" r:id="R98badf0cbf154cfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parser_qa" sheetId="1" r:id="Raf7e2a10596b4dbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -164,8 +164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ParserQa" displayName="ParserQa" ref="A1:S101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ParserQa" displayName="ParserQa" ref="A1:Y101" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="25">
     <x:tableColumn id="1" name="unit_type"/>
     <x:tableColumn id="2" name="query_id"/>
     <x:tableColumn id="3" name="model"/>
@@ -179,12 +179,18 @@
     <x:tableColumn id="11" name="resolved_statute_name"/>
     <x:tableColumn id="12" name="candidate_statute_ids"/>
     <x:tableColumn id="13" name="extraction_correct"/>
-    <x:tableColumn id="14" name="normalization_correct"/>
-    <x:tableColumn id="15" name="statute_mapping_correct"/>
-    <x:tableColumn id="16" name="actually_resolvable"/>
-    <x:tableColumn id="17" name="error_reason"/>
-    <x:tableColumn id="18" name="notes"/>
-    <x:tableColumn id="19" name="audit_unit_id"/>
+    <x:tableColumn id="14" name="law_name_correct"/>
+    <x:tableColumn id="15" name="article_number_correct"/>
+    <x:tableColumn id="16" name="resolution_correct"/>
+    <x:tableColumn id="17" name="normalization_correct"/>
+    <x:tableColumn id="18" name="statute_mapping_correct"/>
+    <x:tableColumn id="19" name="actually_resolvable"/>
+    <x:tableColumn id="20" name="parser_error_type"/>
+    <x:tableColumn id="21" name="confidence"/>
+    <x:tableColumn id="22" name="short_reason"/>
+    <x:tableColumn id="23" name="error_reason"/>
+    <x:tableColumn id="24" name="notes"/>
+    <x:tableColumn id="25" name="audit_unit_id"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -398,12 +404,18 @@
     <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="23" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="23" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="25" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="21" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="24" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="23" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="21" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="19" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="12" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="14" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="42" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="42" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -447,21 +459,39 @@
         <x:v>extraction_correct</x:v>
       </x:c>
       <x:c r="N1" s="15" t="str">
+        <x:v>law_name_correct</x:v>
+      </x:c>
+      <x:c r="O1" s="15" t="str">
+        <x:v>article_number_correct</x:v>
+      </x:c>
+      <x:c r="P1" s="15" t="str">
+        <x:v>resolution_correct</x:v>
+      </x:c>
+      <x:c r="Q1" s="15" t="str">
         <x:v>normalization_correct</x:v>
       </x:c>
-      <x:c r="O1" s="15" t="str">
+      <x:c r="R1" s="15" t="str">
         <x:v>statute_mapping_correct</x:v>
       </x:c>
-      <x:c r="P1" s="15" t="str">
+      <x:c r="S1" s="15" t="str">
         <x:v>actually_resolvable</x:v>
       </x:c>
-      <x:c r="Q1" s="15" t="str">
+      <x:c r="T1" s="15" t="str">
+        <x:v>parser_error_type</x:v>
+      </x:c>
+      <x:c r="U1" s="15" t="str">
+        <x:v>confidence</x:v>
+      </x:c>
+      <x:c r="V1" s="15" t="str">
+        <x:v>short_reason</x:v>
+      </x:c>
+      <x:c r="W1" s="15" t="str">
         <x:v>error_reason</x:v>
       </x:c>
-      <x:c r="R1" s="15" t="str">
+      <x:c r="X1" s="15" t="str">
         <x:v>notes</x:v>
       </x:c>
-      <x:c r="S1" s="16" t="str">
+      <x:c r="Y1" s="16" t="str">
         <x:v>audit_unit_id</x:v>
       </x:c>
     </x:row>
@@ -513,7 +543,13 @@
       <x:c r="P2" s="18" t="str"/>
       <x:c r="Q2" s="18" t="str"/>
       <x:c r="R2" s="18" t="str"/>
-      <x:c r="S2" s="18" t="n">
+      <x:c r="S2" s="18" t="str"/>
+      <x:c r="T2" s="18" t="str"/>
+      <x:c r="U2" s="18" t="str"/>
+      <x:c r="V2" s="18" t="str"/>
+      <x:c r="W2" s="18" t="str"/>
+      <x:c r="X2" s="18" t="str"/>
+      <x:c r="Y2" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -560,7 +596,13 @@
       <x:c r="P3" s="19" t="str"/>
       <x:c r="Q3" s="19" t="str"/>
       <x:c r="R3" s="19" t="str"/>
-      <x:c r="S3" s="19" t="n">
+      <x:c r="S3" s="19" t="str"/>
+      <x:c r="T3" s="19" t="str"/>
+      <x:c r="U3" s="19" t="str"/>
+      <x:c r="V3" s="19" t="str"/>
+      <x:c r="W3" s="19" t="str"/>
+      <x:c r="X3" s="19" t="str"/>
+      <x:c r="Y3" s="19" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -607,7 +649,13 @@
       <x:c r="P4" s="19" t="str"/>
       <x:c r="Q4" s="19" t="str"/>
       <x:c r="R4" s="19" t="str"/>
-      <x:c r="S4" s="19" t="n">
+      <x:c r="S4" s="19" t="str"/>
+      <x:c r="T4" s="19" t="str"/>
+      <x:c r="U4" s="19" t="str"/>
+      <x:c r="V4" s="19" t="str"/>
+      <x:c r="W4" s="19" t="str"/>
+      <x:c r="X4" s="19" t="str"/>
+      <x:c r="Y4" s="19" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -654,7 +702,13 @@
       <x:c r="P5" s="19" t="str"/>
       <x:c r="Q5" s="19" t="str"/>
       <x:c r="R5" s="19" t="str"/>
-      <x:c r="S5" s="19" t="n">
+      <x:c r="S5" s="19" t="str"/>
+      <x:c r="T5" s="19" t="str"/>
+      <x:c r="U5" s="19" t="str"/>
+      <x:c r="V5" s="19" t="str"/>
+      <x:c r="W5" s="19" t="str"/>
+      <x:c r="X5" s="19" t="str"/>
+      <x:c r="Y5" s="19" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -701,7 +755,13 @@
       <x:c r="P6" s="19" t="str"/>
       <x:c r="Q6" s="19" t="str"/>
       <x:c r="R6" s="19" t="str"/>
-      <x:c r="S6" s="19" t="n">
+      <x:c r="S6" s="19" t="str"/>
+      <x:c r="T6" s="19" t="str"/>
+      <x:c r="U6" s="19" t="str"/>
+      <x:c r="V6" s="19" t="str"/>
+      <x:c r="W6" s="19" t="str"/>
+      <x:c r="X6" s="19" t="str"/>
+      <x:c r="Y6" s="19" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -752,7 +812,13 @@
       <x:c r="P7" s="19" t="str"/>
       <x:c r="Q7" s="19" t="str"/>
       <x:c r="R7" s="19" t="str"/>
-      <x:c r="S7" s="19" t="n">
+      <x:c r="S7" s="19" t="str"/>
+      <x:c r="T7" s="19" t="str"/>
+      <x:c r="U7" s="19" t="str"/>
+      <x:c r="V7" s="19" t="str"/>
+      <x:c r="W7" s="19" t="str"/>
+      <x:c r="X7" s="19" t="str"/>
+      <x:c r="Y7" s="19" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -799,7 +865,13 @@
       <x:c r="P8" s="19" t="str"/>
       <x:c r="Q8" s="19" t="str"/>
       <x:c r="R8" s="19" t="str"/>
-      <x:c r="S8" s="19" t="n">
+      <x:c r="S8" s="19" t="str"/>
+      <x:c r="T8" s="19" t="str"/>
+      <x:c r="U8" s="19" t="str"/>
+      <x:c r="V8" s="19" t="str"/>
+      <x:c r="W8" s="19" t="str"/>
+      <x:c r="X8" s="19" t="str"/>
+      <x:c r="Y8" s="19" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -846,7 +918,13 @@
       <x:c r="P9" s="19" t="str"/>
       <x:c r="Q9" s="19" t="str"/>
       <x:c r="R9" s="19" t="str"/>
-      <x:c r="S9" s="19" t="n">
+      <x:c r="S9" s="19" t="str"/>
+      <x:c r="T9" s="19" t="str"/>
+      <x:c r="U9" s="19" t="str"/>
+      <x:c r="V9" s="19" t="str"/>
+      <x:c r="W9" s="19" t="str"/>
+      <x:c r="X9" s="19" t="str"/>
+      <x:c r="Y9" s="19" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -898,7 +976,13 @@
       <x:c r="P10" s="19" t="str"/>
       <x:c r="Q10" s="19" t="str"/>
       <x:c r="R10" s="19" t="str"/>
-      <x:c r="S10" s="19" t="n">
+      <x:c r="S10" s="19" t="str"/>
+      <x:c r="T10" s="19" t="str"/>
+      <x:c r="U10" s="19" t="str"/>
+      <x:c r="V10" s="19" t="str"/>
+      <x:c r="W10" s="19" t="str"/>
+      <x:c r="X10" s="19" t="str"/>
+      <x:c r="Y10" s="19" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -946,7 +1030,13 @@
       <x:c r="P11" s="19" t="str"/>
       <x:c r="Q11" s="19" t="str"/>
       <x:c r="R11" s="19" t="str"/>
-      <x:c r="S11" s="19" t="n">
+      <x:c r="S11" s="19" t="str"/>
+      <x:c r="T11" s="19" t="str"/>
+      <x:c r="U11" s="19" t="str"/>
+      <x:c r="V11" s="19" t="str"/>
+      <x:c r="W11" s="19" t="str"/>
+      <x:c r="X11" s="19" t="str"/>
+      <x:c r="Y11" s="19" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -998,7 +1088,13 @@
       <x:c r="P12" s="19" t="str"/>
       <x:c r="Q12" s="19" t="str"/>
       <x:c r="R12" s="19" t="str"/>
-      <x:c r="S12" s="19" t="n">
+      <x:c r="S12" s="19" t="str"/>
+      <x:c r="T12" s="19" t="str"/>
+      <x:c r="U12" s="19" t="str"/>
+      <x:c r="V12" s="19" t="str"/>
+      <x:c r="W12" s="19" t="str"/>
+      <x:c r="X12" s="19" t="str"/>
+      <x:c r="Y12" s="19" t="n">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -1059,7 +1155,13 @@
       <x:c r="P13" s="19" t="str"/>
       <x:c r="Q13" s="19" t="str"/>
       <x:c r="R13" s="19" t="str"/>
-      <x:c r="S13" s="19" t="n">
+      <x:c r="S13" s="19" t="str"/>
+      <x:c r="T13" s="19" t="str"/>
+      <x:c r="U13" s="19" t="str"/>
+      <x:c r="V13" s="19" t="str"/>
+      <x:c r="W13" s="19" t="str"/>
+      <x:c r="X13" s="19" t="str"/>
+      <x:c r="Y13" s="19" t="n">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -1108,7 +1210,13 @@
       <x:c r="P14" s="19" t="str"/>
       <x:c r="Q14" s="19" t="str"/>
       <x:c r="R14" s="19" t="str"/>
-      <x:c r="S14" s="19" t="n">
+      <x:c r="S14" s="19" t="str"/>
+      <x:c r="T14" s="19" t="str"/>
+      <x:c r="U14" s="19" t="str"/>
+      <x:c r="V14" s="19" t="str"/>
+      <x:c r="W14" s="19" t="str"/>
+      <x:c r="X14" s="19" t="str"/>
+      <x:c r="Y14" s="19" t="n">
         <x:v>13</x:v>
       </x:c>
     </x:row>
@@ -1155,7 +1263,13 @@
       <x:c r="P15" s="19" t="str"/>
       <x:c r="Q15" s="19" t="str"/>
       <x:c r="R15" s="19" t="str"/>
-      <x:c r="S15" s="19" t="n">
+      <x:c r="S15" s="19" t="str"/>
+      <x:c r="T15" s="19" t="str"/>
+      <x:c r="U15" s="19" t="str"/>
+      <x:c r="V15" s="19" t="str"/>
+      <x:c r="W15" s="19" t="str"/>
+      <x:c r="X15" s="19" t="str"/>
+      <x:c r="Y15" s="19" t="n">
         <x:v>14</x:v>
       </x:c>
     </x:row>
@@ -1206,7 +1320,13 @@
       <x:c r="P16" s="19" t="str"/>
       <x:c r="Q16" s="19" t="str"/>
       <x:c r="R16" s="19" t="str"/>
-      <x:c r="S16" s="19" t="n">
+      <x:c r="S16" s="19" t="str"/>
+      <x:c r="T16" s="19" t="str"/>
+      <x:c r="U16" s="19" t="str"/>
+      <x:c r="V16" s="19" t="str"/>
+      <x:c r="W16" s="19" t="str"/>
+      <x:c r="X16" s="19" t="str"/>
+      <x:c r="Y16" s="19" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -1253,7 +1373,13 @@
       <x:c r="P17" s="19" t="str"/>
       <x:c r="Q17" s="19" t="str"/>
       <x:c r="R17" s="19" t="str"/>
-      <x:c r="S17" s="19" t="n">
+      <x:c r="S17" s="19" t="str"/>
+      <x:c r="T17" s="19" t="str"/>
+      <x:c r="U17" s="19" t="str"/>
+      <x:c r="V17" s="19" t="str"/>
+      <x:c r="W17" s="19" t="str"/>
+      <x:c r="X17" s="19" t="str"/>
+      <x:c r="Y17" s="19" t="n">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -1300,7 +1426,13 @@
       <x:c r="P18" s="19" t="str"/>
       <x:c r="Q18" s="19" t="str"/>
       <x:c r="R18" s="19" t="str"/>
-      <x:c r="S18" s="19" t="n">
+      <x:c r="S18" s="19" t="str"/>
+      <x:c r="T18" s="19" t="str"/>
+      <x:c r="U18" s="19" t="str"/>
+      <x:c r="V18" s="19" t="str"/>
+      <x:c r="W18" s="19" t="str"/>
+      <x:c r="X18" s="19" t="str"/>
+      <x:c r="Y18" s="19" t="n">
         <x:v>17</x:v>
       </x:c>
     </x:row>
@@ -1350,7 +1482,13 @@
       <x:c r="P19" s="19" t="str"/>
       <x:c r="Q19" s="19" t="str"/>
       <x:c r="R19" s="19" t="str"/>
-      <x:c r="S19" s="19" t="n">
+      <x:c r="S19" s="19" t="str"/>
+      <x:c r="T19" s="19" t="str"/>
+      <x:c r="U19" s="19" t="str"/>
+      <x:c r="V19" s="19" t="str"/>
+      <x:c r="W19" s="19" t="str"/>
+      <x:c r="X19" s="19" t="str"/>
+      <x:c r="Y19" s="19" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -1401,7 +1539,13 @@
       <x:c r="P20" s="19" t="str"/>
       <x:c r="Q20" s="19" t="str"/>
       <x:c r="R20" s="19" t="str"/>
-      <x:c r="S20" s="19" t="n">
+      <x:c r="S20" s="19" t="str"/>
+      <x:c r="T20" s="19" t="str"/>
+      <x:c r="U20" s="19" t="str"/>
+      <x:c r="V20" s="19" t="str"/>
+      <x:c r="W20" s="19" t="str"/>
+      <x:c r="X20" s="19" t="str"/>
+      <x:c r="Y20" s="19" t="n">
         <x:v>19</x:v>
       </x:c>
     </x:row>
@@ -1454,7 +1598,13 @@
       <x:c r="P21" s="19" t="str"/>
       <x:c r="Q21" s="19" t="str"/>
       <x:c r="R21" s="19" t="str"/>
-      <x:c r="S21" s="19" t="n">
+      <x:c r="S21" s="19" t="str"/>
+      <x:c r="T21" s="19" t="str"/>
+      <x:c r="U21" s="19" t="str"/>
+      <x:c r="V21" s="19" t="str"/>
+      <x:c r="W21" s="19" t="str"/>
+      <x:c r="X21" s="19" t="str"/>
+      <x:c r="Y21" s="19" t="n">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -1501,7 +1651,13 @@
       <x:c r="P22" s="19" t="str"/>
       <x:c r="Q22" s="19" t="str"/>
       <x:c r="R22" s="19" t="str"/>
-      <x:c r="S22" s="19" t="n">
+      <x:c r="S22" s="19" t="str"/>
+      <x:c r="T22" s="19" t="str"/>
+      <x:c r="U22" s="19" t="str"/>
+      <x:c r="V22" s="19" t="str"/>
+      <x:c r="W22" s="19" t="str"/>
+      <x:c r="X22" s="19" t="str"/>
+      <x:c r="Y22" s="19" t="n">
         <x:v>21</x:v>
       </x:c>
     </x:row>
@@ -1553,7 +1709,13 @@
       <x:c r="P23" s="19" t="str"/>
       <x:c r="Q23" s="19" t="str"/>
       <x:c r="R23" s="19" t="str"/>
-      <x:c r="S23" s="19" t="n">
+      <x:c r="S23" s="19" t="str"/>
+      <x:c r="T23" s="19" t="str"/>
+      <x:c r="U23" s="19" t="str"/>
+      <x:c r="V23" s="19" t="str"/>
+      <x:c r="W23" s="19" t="str"/>
+      <x:c r="X23" s="19" t="str"/>
+      <x:c r="Y23" s="19" t="n">
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -1604,7 +1766,13 @@
       <x:c r="P24" s="19" t="str"/>
       <x:c r="Q24" s="19" t="str"/>
       <x:c r="R24" s="19" t="str"/>
-      <x:c r="S24" s="19" t="n">
+      <x:c r="S24" s="19" t="str"/>
+      <x:c r="T24" s="19" t="str"/>
+      <x:c r="U24" s="19" t="str"/>
+      <x:c r="V24" s="19" t="str"/>
+      <x:c r="W24" s="19" t="str"/>
+      <x:c r="X24" s="19" t="str"/>
+      <x:c r="Y24" s="19" t="n">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -1658,7 +1826,13 @@
       <x:c r="P25" s="19" t="str"/>
       <x:c r="Q25" s="19" t="str"/>
       <x:c r="R25" s="19" t="str"/>
-      <x:c r="S25" s="19" t="n">
+      <x:c r="S25" s="19" t="str"/>
+      <x:c r="T25" s="19" t="str"/>
+      <x:c r="U25" s="19" t="str"/>
+      <x:c r="V25" s="19" t="str"/>
+      <x:c r="W25" s="19" t="str"/>
+      <x:c r="X25" s="19" t="str"/>
+      <x:c r="Y25" s="19" t="n">
         <x:v>24</x:v>
       </x:c>
     </x:row>
@@ -1705,7 +1879,13 @@
       <x:c r="P26" s="19" t="str"/>
       <x:c r="Q26" s="19" t="str"/>
       <x:c r="R26" s="19" t="str"/>
-      <x:c r="S26" s="19" t="n">
+      <x:c r="S26" s="19" t="str"/>
+      <x:c r="T26" s="19" t="str"/>
+      <x:c r="U26" s="19" t="str"/>
+      <x:c r="V26" s="19" t="str"/>
+      <x:c r="W26" s="19" t="str"/>
+      <x:c r="X26" s="19" t="str"/>
+      <x:c r="Y26" s="19" t="n">
         <x:v>25</x:v>
       </x:c>
     </x:row>
@@ -1753,7 +1933,13 @@
       <x:c r="P27" s="19" t="str"/>
       <x:c r="Q27" s="19" t="str"/>
       <x:c r="R27" s="19" t="str"/>
-      <x:c r="S27" s="19" t="n">
+      <x:c r="S27" s="19" t="str"/>
+      <x:c r="T27" s="19" t="str"/>
+      <x:c r="U27" s="19" t="str"/>
+      <x:c r="V27" s="19" t="str"/>
+      <x:c r="W27" s="19" t="str"/>
+      <x:c r="X27" s="19" t="str"/>
+      <x:c r="Y27" s="19" t="n">
         <x:v>26</x:v>
       </x:c>
     </x:row>
@@ -1800,7 +1986,13 @@
       <x:c r="P28" s="19" t="str"/>
       <x:c r="Q28" s="19" t="str"/>
       <x:c r="R28" s="19" t="str"/>
-      <x:c r="S28" s="19" t="n">
+      <x:c r="S28" s="19" t="str"/>
+      <x:c r="T28" s="19" t="str"/>
+      <x:c r="U28" s="19" t="str"/>
+      <x:c r="V28" s="19" t="str"/>
+      <x:c r="W28" s="19" t="str"/>
+      <x:c r="X28" s="19" t="str"/>
+      <x:c r="Y28" s="19" t="n">
         <x:v>27</x:v>
       </x:c>
     </x:row>
@@ -1847,7 +2039,13 @@
       <x:c r="P29" s="19" t="str"/>
       <x:c r="Q29" s="19" t="str"/>
       <x:c r="R29" s="19" t="str"/>
-      <x:c r="S29" s="19" t="n">
+      <x:c r="S29" s="19" t="str"/>
+      <x:c r="T29" s="19" t="str"/>
+      <x:c r="U29" s="19" t="str"/>
+      <x:c r="V29" s="19" t="str"/>
+      <x:c r="W29" s="19" t="str"/>
+      <x:c r="X29" s="19" t="str"/>
+      <x:c r="Y29" s="19" t="n">
         <x:v>28</x:v>
       </x:c>
     </x:row>
@@ -1900,7 +2098,13 @@
       <x:c r="P30" s="19" t="str"/>
       <x:c r="Q30" s="19" t="str"/>
       <x:c r="R30" s="19" t="str"/>
-      <x:c r="S30" s="19" t="n">
+      <x:c r="S30" s="19" t="str"/>
+      <x:c r="T30" s="19" t="str"/>
+      <x:c r="U30" s="19" t="str"/>
+      <x:c r="V30" s="19" t="str"/>
+      <x:c r="W30" s="19" t="str"/>
+      <x:c r="X30" s="19" t="str"/>
+      <x:c r="Y30" s="19" t="n">
         <x:v>29</x:v>
       </x:c>
     </x:row>
@@ -1947,7 +2151,13 @@
       <x:c r="P31" s="19" t="str"/>
       <x:c r="Q31" s="19" t="str"/>
       <x:c r="R31" s="19" t="str"/>
-      <x:c r="S31" s="19" t="n">
+      <x:c r="S31" s="19" t="str"/>
+      <x:c r="T31" s="19" t="str"/>
+      <x:c r="U31" s="19" t="str"/>
+      <x:c r="V31" s="19" t="str"/>
+      <x:c r="W31" s="19" t="str"/>
+      <x:c r="X31" s="19" t="str"/>
+      <x:c r="Y31" s="19" t="n">
         <x:v>30</x:v>
       </x:c>
     </x:row>
@@ -1994,7 +2204,13 @@
       <x:c r="P32" s="19" t="str"/>
       <x:c r="Q32" s="19" t="str"/>
       <x:c r="R32" s="19" t="str"/>
-      <x:c r="S32" s="19" t="n">
+      <x:c r="S32" s="19" t="str"/>
+      <x:c r="T32" s="19" t="str"/>
+      <x:c r="U32" s="19" t="str"/>
+      <x:c r="V32" s="19" t="str"/>
+      <x:c r="W32" s="19" t="str"/>
+      <x:c r="X32" s="19" t="str"/>
+      <x:c r="Y32" s="19" t="n">
         <x:v>31</x:v>
       </x:c>
     </x:row>
@@ -2047,7 +2263,13 @@
       <x:c r="P33" s="19" t="str"/>
       <x:c r="Q33" s="19" t="str"/>
       <x:c r="R33" s="19" t="str"/>
-      <x:c r="S33" s="19" t="n">
+      <x:c r="S33" s="19" t="str"/>
+      <x:c r="T33" s="19" t="str"/>
+      <x:c r="U33" s="19" t="str"/>
+      <x:c r="V33" s="19" t="str"/>
+      <x:c r="W33" s="19" t="str"/>
+      <x:c r="X33" s="19" t="str"/>
+      <x:c r="Y33" s="19" t="n">
         <x:v>32</x:v>
       </x:c>
     </x:row>
@@ -2096,7 +2318,13 @@
       <x:c r="P34" s="19" t="str"/>
       <x:c r="Q34" s="19" t="str"/>
       <x:c r="R34" s="19" t="str"/>
-      <x:c r="S34" s="19" t="n">
+      <x:c r="S34" s="19" t="str"/>
+      <x:c r="T34" s="19" t="str"/>
+      <x:c r="U34" s="19" t="str"/>
+      <x:c r="V34" s="19" t="str"/>
+      <x:c r="W34" s="19" t="str"/>
+      <x:c r="X34" s="19" t="str"/>
+      <x:c r="Y34" s="19" t="n">
         <x:v>33</x:v>
       </x:c>
     </x:row>
@@ -2150,7 +2378,13 @@
       <x:c r="P35" s="19" t="str"/>
       <x:c r="Q35" s="19" t="str"/>
       <x:c r="R35" s="19" t="str"/>
-      <x:c r="S35" s="19" t="n">
+      <x:c r="S35" s="19" t="str"/>
+      <x:c r="T35" s="19" t="str"/>
+      <x:c r="U35" s="19" t="str"/>
+      <x:c r="V35" s="19" t="str"/>
+      <x:c r="W35" s="19" t="str"/>
+      <x:c r="X35" s="19" t="str"/>
+      <x:c r="Y35" s="19" t="n">
         <x:v>34</x:v>
       </x:c>
     </x:row>
@@ -2197,7 +2431,13 @@
       <x:c r="P36" s="19" t="str"/>
       <x:c r="Q36" s="19" t="str"/>
       <x:c r="R36" s="19" t="str"/>
-      <x:c r="S36" s="19" t="n">
+      <x:c r="S36" s="19" t="str"/>
+      <x:c r="T36" s="19" t="str"/>
+      <x:c r="U36" s="19" t="str"/>
+      <x:c r="V36" s="19" t="str"/>
+      <x:c r="W36" s="19" t="str"/>
+      <x:c r="X36" s="19" t="str"/>
+      <x:c r="Y36" s="19" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
@@ -2246,7 +2486,13 @@
       <x:c r="P37" s="19" t="str"/>
       <x:c r="Q37" s="19" t="str"/>
       <x:c r="R37" s="19" t="str"/>
-      <x:c r="S37" s="19" t="n">
+      <x:c r="S37" s="19" t="str"/>
+      <x:c r="T37" s="19" t="str"/>
+      <x:c r="U37" s="19" t="str"/>
+      <x:c r="V37" s="19" t="str"/>
+      <x:c r="W37" s="19" t="str"/>
+      <x:c r="X37" s="19" t="str"/>
+      <x:c r="Y37" s="19" t="n">
         <x:v>36</x:v>
       </x:c>
     </x:row>
@@ -2293,7 +2539,13 @@
       <x:c r="P38" s="19" t="str"/>
       <x:c r="Q38" s="19" t="str"/>
       <x:c r="R38" s="19" t="str"/>
-      <x:c r="S38" s="19" t="n">
+      <x:c r="S38" s="19" t="str"/>
+      <x:c r="T38" s="19" t="str"/>
+      <x:c r="U38" s="19" t="str"/>
+      <x:c r="V38" s="19" t="str"/>
+      <x:c r="W38" s="19" t="str"/>
+      <x:c r="X38" s="19" t="str"/>
+      <x:c r="Y38" s="19" t="n">
         <x:v>37</x:v>
       </x:c>
     </x:row>
@@ -2343,7 +2595,13 @@
       <x:c r="P39" s="19" t="str"/>
       <x:c r="Q39" s="19" t="str"/>
       <x:c r="R39" s="19" t="str"/>
-      <x:c r="S39" s="19" t="n">
+      <x:c r="S39" s="19" t="str"/>
+      <x:c r="T39" s="19" t="str"/>
+      <x:c r="U39" s="19" t="str"/>
+      <x:c r="V39" s="19" t="str"/>
+      <x:c r="W39" s="19" t="str"/>
+      <x:c r="X39" s="19" t="str"/>
+      <x:c r="Y39" s="19" t="n">
         <x:v>38</x:v>
       </x:c>
     </x:row>
@@ -2390,7 +2648,13 @@
       <x:c r="P40" s="19" t="str"/>
       <x:c r="Q40" s="19" t="str"/>
       <x:c r="R40" s="19" t="str"/>
-      <x:c r="S40" s="19" t="n">
+      <x:c r="S40" s="19" t="str"/>
+      <x:c r="T40" s="19" t="str"/>
+      <x:c r="U40" s="19" t="str"/>
+      <x:c r="V40" s="19" t="str"/>
+      <x:c r="W40" s="19" t="str"/>
+      <x:c r="X40" s="19" t="str"/>
+      <x:c r="Y40" s="19" t="n">
         <x:v>39</x:v>
       </x:c>
     </x:row>
@@ -2439,7 +2703,13 @@
       <x:c r="P41" s="19" t="str"/>
       <x:c r="Q41" s="19" t="str"/>
       <x:c r="R41" s="19" t="str"/>
-      <x:c r="S41" s="19" t="n">
+      <x:c r="S41" s="19" t="str"/>
+      <x:c r="T41" s="19" t="str"/>
+      <x:c r="U41" s="19" t="str"/>
+      <x:c r="V41" s="19" t="str"/>
+      <x:c r="W41" s="19" t="str"/>
+      <x:c r="X41" s="19" t="str"/>
+      <x:c r="Y41" s="19" t="n">
         <x:v>40</x:v>
       </x:c>
     </x:row>
@@ -2480,7 +2750,13 @@
       <x:c r="P42" s="19" t="str"/>
       <x:c r="Q42" s="19" t="str"/>
       <x:c r="R42" s="19" t="str"/>
-      <x:c r="S42" s="19" t="n">
+      <x:c r="S42" s="19" t="str"/>
+      <x:c r="T42" s="19" t="str"/>
+      <x:c r="U42" s="19" t="str"/>
+      <x:c r="V42" s="19" t="str"/>
+      <x:c r="W42" s="19" t="str"/>
+      <x:c r="X42" s="19" t="str"/>
+      <x:c r="Y42" s="19" t="n">
         <x:v>41</x:v>
       </x:c>
     </x:row>
@@ -2530,7 +2806,13 @@
       <x:c r="P43" s="19" t="str"/>
       <x:c r="Q43" s="19" t="str"/>
       <x:c r="R43" s="19" t="str"/>
-      <x:c r="S43" s="19" t="n">
+      <x:c r="S43" s="19" t="str"/>
+      <x:c r="T43" s="19" t="str"/>
+      <x:c r="U43" s="19" t="str"/>
+      <x:c r="V43" s="19" t="str"/>
+      <x:c r="W43" s="19" t="str"/>
+      <x:c r="X43" s="19" t="str"/>
+      <x:c r="Y43" s="19" t="n">
         <x:v>42</x:v>
       </x:c>
     </x:row>
@@ -2584,7 +2866,13 @@
       <x:c r="P44" s="19" t="str"/>
       <x:c r="Q44" s="19" t="str"/>
       <x:c r="R44" s="19" t="str"/>
-      <x:c r="S44" s="19" t="n">
+      <x:c r="S44" s="19" t="str"/>
+      <x:c r="T44" s="19" t="str"/>
+      <x:c r="U44" s="19" t="str"/>
+      <x:c r="V44" s="19" t="str"/>
+      <x:c r="W44" s="19" t="str"/>
+      <x:c r="X44" s="19" t="str"/>
+      <x:c r="Y44" s="19" t="n">
         <x:v>43</x:v>
       </x:c>
     </x:row>
@@ -2632,7 +2920,13 @@
       <x:c r="P45" s="19" t="str"/>
       <x:c r="Q45" s="19" t="str"/>
       <x:c r="R45" s="19" t="str"/>
-      <x:c r="S45" s="19" t="n">
+      <x:c r="S45" s="19" t="str"/>
+      <x:c r="T45" s="19" t="str"/>
+      <x:c r="U45" s="19" t="str"/>
+      <x:c r="V45" s="19" t="str"/>
+      <x:c r="W45" s="19" t="str"/>
+      <x:c r="X45" s="19" t="str"/>
+      <x:c r="Y45" s="19" t="n">
         <x:v>44</x:v>
       </x:c>
     </x:row>
@@ -2673,7 +2967,13 @@
       <x:c r="P46" s="19" t="str"/>
       <x:c r="Q46" s="19" t="str"/>
       <x:c r="R46" s="19" t="str"/>
-      <x:c r="S46" s="19" t="n">
+      <x:c r="S46" s="19" t="str"/>
+      <x:c r="T46" s="19" t="str"/>
+      <x:c r="U46" s="19" t="str"/>
+      <x:c r="V46" s="19" t="str"/>
+      <x:c r="W46" s="19" t="str"/>
+      <x:c r="X46" s="19" t="str"/>
+      <x:c r="Y46" s="19" t="n">
         <x:v>45</x:v>
       </x:c>
     </x:row>
@@ -2716,7 +3016,13 @@
       <x:c r="P47" s="19" t="str"/>
       <x:c r="Q47" s="19" t="str"/>
       <x:c r="R47" s="19" t="str"/>
-      <x:c r="S47" s="19" t="n">
+      <x:c r="S47" s="19" t="str"/>
+      <x:c r="T47" s="19" t="str"/>
+      <x:c r="U47" s="19" t="str"/>
+      <x:c r="V47" s="19" t="str"/>
+      <x:c r="W47" s="19" t="str"/>
+      <x:c r="X47" s="19" t="str"/>
+      <x:c r="Y47" s="19" t="n">
         <x:v>46</x:v>
       </x:c>
     </x:row>
@@ -2769,7 +3075,13 @@
       <x:c r="P48" s="19" t="str"/>
       <x:c r="Q48" s="19" t="str"/>
       <x:c r="R48" s="19" t="str"/>
-      <x:c r="S48" s="19" t="n">
+      <x:c r="S48" s="19" t="str"/>
+      <x:c r="T48" s="19" t="str"/>
+      <x:c r="U48" s="19" t="str"/>
+      <x:c r="V48" s="19" t="str"/>
+      <x:c r="W48" s="19" t="str"/>
+      <x:c r="X48" s="19" t="str"/>
+      <x:c r="Y48" s="19" t="n">
         <x:v>47</x:v>
       </x:c>
     </x:row>
@@ -2824,7 +3136,13 @@
       <x:c r="P49" s="19" t="str"/>
       <x:c r="Q49" s="19" t="str"/>
       <x:c r="R49" s="19" t="str"/>
-      <x:c r="S49" s="19" t="n">
+      <x:c r="S49" s="19" t="str"/>
+      <x:c r="T49" s="19" t="str"/>
+      <x:c r="U49" s="19" t="str"/>
+      <x:c r="V49" s="19" t="str"/>
+      <x:c r="W49" s="19" t="str"/>
+      <x:c r="X49" s="19" t="str"/>
+      <x:c r="Y49" s="19" t="n">
         <x:v>48</x:v>
       </x:c>
     </x:row>
@@ -2871,7 +3189,13 @@
       <x:c r="P50" s="19" t="str"/>
       <x:c r="Q50" s="19" t="str"/>
       <x:c r="R50" s="19" t="str"/>
-      <x:c r="S50" s="19" t="n">
+      <x:c r="S50" s="19" t="str"/>
+      <x:c r="T50" s="19" t="str"/>
+      <x:c r="U50" s="19" t="str"/>
+      <x:c r="V50" s="19" t="str"/>
+      <x:c r="W50" s="19" t="str"/>
+      <x:c r="X50" s="19" t="str"/>
+      <x:c r="Y50" s="19" t="n">
         <x:v>49</x:v>
       </x:c>
     </x:row>
@@ -2912,7 +3236,13 @@
       <x:c r="P51" s="19" t="str"/>
       <x:c r="Q51" s="19" t="str"/>
       <x:c r="R51" s="19" t="str"/>
-      <x:c r="S51" s="19" t="n">
+      <x:c r="S51" s="19" t="str"/>
+      <x:c r="T51" s="19" t="str"/>
+      <x:c r="U51" s="19" t="str"/>
+      <x:c r="V51" s="19" t="str"/>
+      <x:c r="W51" s="19" t="str"/>
+      <x:c r="X51" s="19" t="str"/>
+      <x:c r="Y51" s="19" t="n">
         <x:v>50</x:v>
       </x:c>
     </x:row>
@@ -2953,7 +3283,13 @@
       <x:c r="P52" s="19" t="str"/>
       <x:c r="Q52" s="19" t="str"/>
       <x:c r="R52" s="19" t="str"/>
-      <x:c r="S52" s="19" t="n">
+      <x:c r="S52" s="19" t="str"/>
+      <x:c r="T52" s="19" t="str"/>
+      <x:c r="U52" s="19" t="str"/>
+      <x:c r="V52" s="19" t="str"/>
+      <x:c r="W52" s="19" t="str"/>
+      <x:c r="X52" s="19" t="str"/>
+      <x:c r="Y52" s="19" t="n">
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -2996,7 +3332,13 @@
       <x:c r="P53" s="19" t="str"/>
       <x:c r="Q53" s="19" t="str"/>
       <x:c r="R53" s="19" t="str"/>
-      <x:c r="S53" s="19" t="n">
+      <x:c r="S53" s="19" t="str"/>
+      <x:c r="T53" s="19" t="str"/>
+      <x:c r="U53" s="19" t="str"/>
+      <x:c r="V53" s="19" t="str"/>
+      <x:c r="W53" s="19" t="str"/>
+      <x:c r="X53" s="19" t="str"/>
+      <x:c r="Y53" s="19" t="n">
         <x:v>52</x:v>
       </x:c>
     </x:row>
@@ -3037,7 +3379,13 @@
       <x:c r="P54" s="19" t="str"/>
       <x:c r="Q54" s="19" t="str"/>
       <x:c r="R54" s="19" t="str"/>
-      <x:c r="S54" s="19" t="n">
+      <x:c r="S54" s="19" t="str"/>
+      <x:c r="T54" s="19" t="str"/>
+      <x:c r="U54" s="19" t="str"/>
+      <x:c r="V54" s="19" t="str"/>
+      <x:c r="W54" s="19" t="str"/>
+      <x:c r="X54" s="19" t="str"/>
+      <x:c r="Y54" s="19" t="n">
         <x:v>53</x:v>
       </x:c>
     </x:row>
@@ -3081,7 +3429,13 @@
       <x:c r="P55" s="19" t="str"/>
       <x:c r="Q55" s="19" t="str"/>
       <x:c r="R55" s="19" t="str"/>
-      <x:c r="S55" s="19" t="n">
+      <x:c r="S55" s="19" t="str"/>
+      <x:c r="T55" s="19" t="str"/>
+      <x:c r="U55" s="19" t="str"/>
+      <x:c r="V55" s="19" t="str"/>
+      <x:c r="W55" s="19" t="str"/>
+      <x:c r="X55" s="19" t="str"/>
+      <x:c r="Y55" s="19" t="n">
         <x:v>54</x:v>
       </x:c>
     </x:row>
@@ -3130,7 +3484,13 @@
       <x:c r="P56" s="19" t="str"/>
       <x:c r="Q56" s="19" t="str"/>
       <x:c r="R56" s="19" t="str"/>
-      <x:c r="S56" s="19" t="n">
+      <x:c r="S56" s="19" t="str"/>
+      <x:c r="T56" s="19" t="str"/>
+      <x:c r="U56" s="19" t="str"/>
+      <x:c r="V56" s="19" t="str"/>
+      <x:c r="W56" s="19" t="str"/>
+      <x:c r="X56" s="19" t="str"/>
+      <x:c r="Y56" s="19" t="n">
         <x:v>55</x:v>
       </x:c>
     </x:row>
@@ -3181,7 +3541,13 @@
       <x:c r="P57" s="19" t="str"/>
       <x:c r="Q57" s="19" t="str"/>
       <x:c r="R57" s="19" t="str"/>
-      <x:c r="S57" s="19" t="n">
+      <x:c r="S57" s="19" t="str"/>
+      <x:c r="T57" s="19" t="str"/>
+      <x:c r="U57" s="19" t="str"/>
+      <x:c r="V57" s="19" t="str"/>
+      <x:c r="W57" s="19" t="str"/>
+      <x:c r="X57" s="19" t="str"/>
+      <x:c r="Y57" s="19" t="n">
         <x:v>56</x:v>
       </x:c>
     </x:row>
@@ -3226,7 +3592,13 @@
       <x:c r="P58" s="19" t="str"/>
       <x:c r="Q58" s="19" t="str"/>
       <x:c r="R58" s="19" t="str"/>
-      <x:c r="S58" s="19" t="n">
+      <x:c r="S58" s="19" t="str"/>
+      <x:c r="T58" s="19" t="str"/>
+      <x:c r="U58" s="19" t="str"/>
+      <x:c r="V58" s="19" t="str"/>
+      <x:c r="W58" s="19" t="str"/>
+      <x:c r="X58" s="19" t="str"/>
+      <x:c r="Y58" s="19" t="n">
         <x:v>57</x:v>
       </x:c>
     </x:row>
@@ -3274,7 +3646,13 @@
       <x:c r="P59" s="19" t="str"/>
       <x:c r="Q59" s="19" t="str"/>
       <x:c r="R59" s="19" t="str"/>
-      <x:c r="S59" s="19" t="n">
+      <x:c r="S59" s="19" t="str"/>
+      <x:c r="T59" s="19" t="str"/>
+      <x:c r="U59" s="19" t="str"/>
+      <x:c r="V59" s="19" t="str"/>
+      <x:c r="W59" s="19" t="str"/>
+      <x:c r="X59" s="19" t="str"/>
+      <x:c r="Y59" s="19" t="n">
         <x:v>58</x:v>
       </x:c>
     </x:row>
@@ -3315,7 +3693,13 @@
       <x:c r="P60" s="19" t="str"/>
       <x:c r="Q60" s="19" t="str"/>
       <x:c r="R60" s="19" t="str"/>
-      <x:c r="S60" s="19" t="n">
+      <x:c r="S60" s="19" t="str"/>
+      <x:c r="T60" s="19" t="str"/>
+      <x:c r="U60" s="19" t="str"/>
+      <x:c r="V60" s="19" t="str"/>
+      <x:c r="W60" s="19" t="str"/>
+      <x:c r="X60" s="19" t="str"/>
+      <x:c r="Y60" s="19" t="n">
         <x:v>59</x:v>
       </x:c>
     </x:row>
@@ -3356,7 +3740,13 @@
       <x:c r="P61" s="19" t="str"/>
       <x:c r="Q61" s="19" t="str"/>
       <x:c r="R61" s="19" t="str"/>
-      <x:c r="S61" s="19" t="n">
+      <x:c r="S61" s="19" t="str"/>
+      <x:c r="T61" s="19" t="str"/>
+      <x:c r="U61" s="19" t="str"/>
+      <x:c r="V61" s="19" t="str"/>
+      <x:c r="W61" s="19" t="str"/>
+      <x:c r="X61" s="19" t="str"/>
+      <x:c r="Y61" s="19" t="n">
         <x:v>60</x:v>
       </x:c>
     </x:row>
@@ -3400,7 +3790,13 @@
       <x:c r="P62" s="19" t="str"/>
       <x:c r="Q62" s="19" t="str"/>
       <x:c r="R62" s="19" t="str"/>
-      <x:c r="S62" s="19" t="n">
+      <x:c r="S62" s="19" t="str"/>
+      <x:c r="T62" s="19" t="str"/>
+      <x:c r="U62" s="19" t="str"/>
+      <x:c r="V62" s="19" t="str"/>
+      <x:c r="W62" s="19" t="str"/>
+      <x:c r="X62" s="19" t="str"/>
+      <x:c r="Y62" s="19" t="n">
         <x:v>61</x:v>
       </x:c>
     </x:row>
@@ -3456,7 +3852,13 @@
       <x:c r="P63" s="19" t="str"/>
       <x:c r="Q63" s="19" t="str"/>
       <x:c r="R63" s="19" t="str"/>
-      <x:c r="S63" s="19" t="n">
+      <x:c r="S63" s="19" t="str"/>
+      <x:c r="T63" s="19" t="str"/>
+      <x:c r="U63" s="19" t="str"/>
+      <x:c r="V63" s="19" t="str"/>
+      <x:c r="W63" s="19" t="str"/>
+      <x:c r="X63" s="19" t="str"/>
+      <x:c r="Y63" s="19" t="n">
         <x:v>62</x:v>
       </x:c>
     </x:row>
@@ -3502,7 +3904,13 @@
       <x:c r="P64" s="19" t="str"/>
       <x:c r="Q64" s="19" t="str"/>
       <x:c r="R64" s="19" t="str"/>
-      <x:c r="S64" s="19" t="n">
+      <x:c r="S64" s="19" t="str"/>
+      <x:c r="T64" s="19" t="str"/>
+      <x:c r="U64" s="19" t="str"/>
+      <x:c r="V64" s="19" t="str"/>
+      <x:c r="W64" s="19" t="str"/>
+      <x:c r="X64" s="19" t="str"/>
+      <x:c r="Y64" s="19" t="n">
         <x:v>63</x:v>
       </x:c>
     </x:row>
@@ -3543,7 +3951,13 @@
       <x:c r="P65" s="19" t="str"/>
       <x:c r="Q65" s="19" t="str"/>
       <x:c r="R65" s="19" t="str"/>
-      <x:c r="S65" s="19" t="n">
+      <x:c r="S65" s="19" t="str"/>
+      <x:c r="T65" s="19" t="str"/>
+      <x:c r="U65" s="19" t="str"/>
+      <x:c r="V65" s="19" t="str"/>
+      <x:c r="W65" s="19" t="str"/>
+      <x:c r="X65" s="19" t="str"/>
+      <x:c r="Y65" s="19" t="n">
         <x:v>64</x:v>
       </x:c>
     </x:row>
@@ -3591,7 +4005,13 @@
       <x:c r="P66" s="19" t="str"/>
       <x:c r="Q66" s="19" t="str"/>
       <x:c r="R66" s="19" t="str"/>
-      <x:c r="S66" s="19" t="n">
+      <x:c r="S66" s="19" t="str"/>
+      <x:c r="T66" s="19" t="str"/>
+      <x:c r="U66" s="19" t="str"/>
+      <x:c r="V66" s="19" t="str"/>
+      <x:c r="W66" s="19" t="str"/>
+      <x:c r="X66" s="19" t="str"/>
+      <x:c r="Y66" s="19" t="n">
         <x:v>65</x:v>
       </x:c>
     </x:row>
@@ -3632,7 +4052,13 @@
       <x:c r="P67" s="19" t="str"/>
       <x:c r="Q67" s="19" t="str"/>
       <x:c r="R67" s="19" t="str"/>
-      <x:c r="S67" s="19" t="n">
+      <x:c r="S67" s="19" t="str"/>
+      <x:c r="T67" s="19" t="str"/>
+      <x:c r="U67" s="19" t="str"/>
+      <x:c r="V67" s="19" t="str"/>
+      <x:c r="W67" s="19" t="str"/>
+      <x:c r="X67" s="19" t="str"/>
+      <x:c r="Y67" s="19" t="n">
         <x:v>66</x:v>
       </x:c>
     </x:row>
@@ -3673,7 +4099,13 @@
       <x:c r="P68" s="19" t="str"/>
       <x:c r="Q68" s="19" t="str"/>
       <x:c r="R68" s="19" t="str"/>
-      <x:c r="S68" s="19" t="n">
+      <x:c r="S68" s="19" t="str"/>
+      <x:c r="T68" s="19" t="str"/>
+      <x:c r="U68" s="19" t="str"/>
+      <x:c r="V68" s="19" t="str"/>
+      <x:c r="W68" s="19" t="str"/>
+      <x:c r="X68" s="19" t="str"/>
+      <x:c r="Y68" s="19" t="n">
         <x:v>67</x:v>
       </x:c>
     </x:row>
@@ -3715,7 +4147,13 @@
       <x:c r="P69" s="19" t="str"/>
       <x:c r="Q69" s="19" t="str"/>
       <x:c r="R69" s="19" t="str"/>
-      <x:c r="S69" s="19" t="n">
+      <x:c r="S69" s="19" t="str"/>
+      <x:c r="T69" s="19" t="str"/>
+      <x:c r="U69" s="19" t="str"/>
+      <x:c r="V69" s="19" t="str"/>
+      <x:c r="W69" s="19" t="str"/>
+      <x:c r="X69" s="19" t="str"/>
+      <x:c r="Y69" s="19" t="n">
         <x:v>68</x:v>
       </x:c>
     </x:row>
@@ -3758,7 +4196,13 @@
       <x:c r="P70" s="19" t="str"/>
       <x:c r="Q70" s="19" t="str"/>
       <x:c r="R70" s="19" t="str"/>
-      <x:c r="S70" s="19" t="n">
+      <x:c r="S70" s="19" t="str"/>
+      <x:c r="T70" s="19" t="str"/>
+      <x:c r="U70" s="19" t="str"/>
+      <x:c r="V70" s="19" t="str"/>
+      <x:c r="W70" s="19" t="str"/>
+      <x:c r="X70" s="19" t="str"/>
+      <x:c r="Y70" s="19" t="n">
         <x:v>69</x:v>
       </x:c>
     </x:row>
@@ -3807,7 +4251,13 @@
       <x:c r="P71" s="19" t="str"/>
       <x:c r="Q71" s="19" t="str"/>
       <x:c r="R71" s="19" t="str"/>
-      <x:c r="S71" s="19" t="n">
+      <x:c r="S71" s="19" t="str"/>
+      <x:c r="T71" s="19" t="str"/>
+      <x:c r="U71" s="19" t="str"/>
+      <x:c r="V71" s="19" t="str"/>
+      <x:c r="W71" s="19" t="str"/>
+      <x:c r="X71" s="19" t="str"/>
+      <x:c r="Y71" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
     </x:row>
@@ -3856,7 +4306,13 @@
       <x:c r="P72" s="19" t="str"/>
       <x:c r="Q72" s="19" t="str"/>
       <x:c r="R72" s="19" t="str"/>
-      <x:c r="S72" s="19" t="n">
+      <x:c r="S72" s="19" t="str"/>
+      <x:c r="T72" s="19" t="str"/>
+      <x:c r="U72" s="19" t="str"/>
+      <x:c r="V72" s="19" t="str"/>
+      <x:c r="W72" s="19" t="str"/>
+      <x:c r="X72" s="19" t="str"/>
+      <x:c r="Y72" s="19" t="n">
         <x:v>71</x:v>
       </x:c>
     </x:row>
@@ -3899,7 +4355,13 @@
       <x:c r="P73" s="19" t="str"/>
       <x:c r="Q73" s="19" t="str"/>
       <x:c r="R73" s="19" t="str"/>
-      <x:c r="S73" s="19" t="n">
+      <x:c r="S73" s="19" t="str"/>
+      <x:c r="T73" s="19" t="str"/>
+      <x:c r="U73" s="19" t="str"/>
+      <x:c r="V73" s="19" t="str"/>
+      <x:c r="W73" s="19" t="str"/>
+      <x:c r="X73" s="19" t="str"/>
+      <x:c r="Y73" s="19" t="n">
         <x:v>72</x:v>
       </x:c>
     </x:row>
@@ -3943,7 +4405,13 @@
       <x:c r="P74" s="19" t="str"/>
       <x:c r="Q74" s="19" t="str"/>
       <x:c r="R74" s="19" t="str"/>
-      <x:c r="S74" s="19" t="n">
+      <x:c r="S74" s="19" t="str"/>
+      <x:c r="T74" s="19" t="str"/>
+      <x:c r="U74" s="19" t="str"/>
+      <x:c r="V74" s="19" t="str"/>
+      <x:c r="W74" s="19" t="str"/>
+      <x:c r="X74" s="19" t="str"/>
+      <x:c r="Y74" s="19" t="n">
         <x:v>73</x:v>
       </x:c>
     </x:row>
@@ -3985,7 +4453,13 @@
       <x:c r="P75" s="19" t="str"/>
       <x:c r="Q75" s="19" t="str"/>
       <x:c r="R75" s="19" t="str"/>
-      <x:c r="S75" s="19" t="n">
+      <x:c r="S75" s="19" t="str"/>
+      <x:c r="T75" s="19" t="str"/>
+      <x:c r="U75" s="19" t="str"/>
+      <x:c r="V75" s="19" t="str"/>
+      <x:c r="W75" s="19" t="str"/>
+      <x:c r="X75" s="19" t="str"/>
+      <x:c r="Y75" s="19" t="n">
         <x:v>74</x:v>
       </x:c>
     </x:row>
@@ -4033,7 +4507,13 @@
       <x:c r="P76" s="19" t="str"/>
       <x:c r="Q76" s="19" t="str"/>
       <x:c r="R76" s="19" t="str"/>
-      <x:c r="S76" s="19" t="n">
+      <x:c r="S76" s="19" t="str"/>
+      <x:c r="T76" s="19" t="str"/>
+      <x:c r="U76" s="19" t="str"/>
+      <x:c r="V76" s="19" t="str"/>
+      <x:c r="W76" s="19" t="str"/>
+      <x:c r="X76" s="19" t="str"/>
+      <x:c r="Y76" s="19" t="n">
         <x:v>75</x:v>
       </x:c>
     </x:row>
@@ -4075,7 +4555,13 @@
       <x:c r="P77" s="19" t="str"/>
       <x:c r="Q77" s="19" t="str"/>
       <x:c r="R77" s="19" t="str"/>
-      <x:c r="S77" s="19" t="n">
+      <x:c r="S77" s="19" t="str"/>
+      <x:c r="T77" s="19" t="str"/>
+      <x:c r="U77" s="19" t="str"/>
+      <x:c r="V77" s="19" t="str"/>
+      <x:c r="W77" s="19" t="str"/>
+      <x:c r="X77" s="19" t="str"/>
+      <x:c r="Y77" s="19" t="n">
         <x:v>76</x:v>
       </x:c>
     </x:row>
@@ -4120,7 +4606,13 @@
       <x:c r="P78" s="19" t="str"/>
       <x:c r="Q78" s="19" t="str"/>
       <x:c r="R78" s="19" t="str"/>
-      <x:c r="S78" s="19" t="n">
+      <x:c r="S78" s="19" t="str"/>
+      <x:c r="T78" s="19" t="str"/>
+      <x:c r="U78" s="19" t="str"/>
+      <x:c r="V78" s="19" t="str"/>
+      <x:c r="W78" s="19" t="str"/>
+      <x:c r="X78" s="19" t="str"/>
+      <x:c r="Y78" s="19" t="n">
         <x:v>77</x:v>
       </x:c>
     </x:row>
@@ -4168,7 +4660,13 @@
       <x:c r="P79" s="19" t="str"/>
       <x:c r="Q79" s="19" t="str"/>
       <x:c r="R79" s="19" t="str"/>
-      <x:c r="S79" s="19" t="n">
+      <x:c r="S79" s="19" t="str"/>
+      <x:c r="T79" s="19" t="str"/>
+      <x:c r="U79" s="19" t="str"/>
+      <x:c r="V79" s="19" t="str"/>
+      <x:c r="W79" s="19" t="str"/>
+      <x:c r="X79" s="19" t="str"/>
+      <x:c r="Y79" s="19" t="n">
         <x:v>78</x:v>
       </x:c>
     </x:row>
@@ -4216,7 +4714,13 @@
       <x:c r="P80" s="19" t="str"/>
       <x:c r="Q80" s="19" t="str"/>
       <x:c r="R80" s="19" t="str"/>
-      <x:c r="S80" s="19" t="n">
+      <x:c r="S80" s="19" t="str"/>
+      <x:c r="T80" s="19" t="str"/>
+      <x:c r="U80" s="19" t="str"/>
+      <x:c r="V80" s="19" t="str"/>
+      <x:c r="W80" s="19" t="str"/>
+      <x:c r="X80" s="19" t="str"/>
+      <x:c r="Y80" s="19" t="n">
         <x:v>79</x:v>
       </x:c>
     </x:row>
@@ -4265,7 +4769,13 @@
       <x:c r="P81" s="19" t="str"/>
       <x:c r="Q81" s="19" t="str"/>
       <x:c r="R81" s="19" t="str"/>
-      <x:c r="S81" s="19" t="n">
+      <x:c r="S81" s="19" t="str"/>
+      <x:c r="T81" s="19" t="str"/>
+      <x:c r="U81" s="19" t="str"/>
+      <x:c r="V81" s="19" t="str"/>
+      <x:c r="W81" s="19" t="str"/>
+      <x:c r="X81" s="19" t="str"/>
+      <x:c r="Y81" s="19" t="n">
         <x:v>80</x:v>
       </x:c>
     </x:row>
@@ -4302,7 +4812,13 @@
       <x:c r="P82" s="19" t="str"/>
       <x:c r="Q82" s="19" t="str"/>
       <x:c r="R82" s="19" t="str"/>
-      <x:c r="S82" s="19" t="n">
+      <x:c r="S82" s="19" t="str"/>
+      <x:c r="T82" s="19" t="str"/>
+      <x:c r="U82" s="19" t="str"/>
+      <x:c r="V82" s="19" t="str"/>
+      <x:c r="W82" s="19" t="str"/>
+      <x:c r="X82" s="19" t="str"/>
+      <x:c r="Y82" s="19" t="n">
         <x:v>81</x:v>
       </x:c>
     </x:row>
@@ -4345,7 +4861,13 @@
       <x:c r="P83" s="19" t="str"/>
       <x:c r="Q83" s="19" t="str"/>
       <x:c r="R83" s="19" t="str"/>
-      <x:c r="S83" s="19" t="n">
+      <x:c r="S83" s="19" t="str"/>
+      <x:c r="T83" s="19" t="str"/>
+      <x:c r="U83" s="19" t="str"/>
+      <x:c r="V83" s="19" t="str"/>
+      <x:c r="W83" s="19" t="str"/>
+      <x:c r="X83" s="19" t="str"/>
+      <x:c r="Y83" s="19" t="n">
         <x:v>82</x:v>
       </x:c>
     </x:row>
@@ -4386,7 +4908,13 @@
       <x:c r="P84" s="19" t="str"/>
       <x:c r="Q84" s="19" t="str"/>
       <x:c r="R84" s="19" t="str"/>
-      <x:c r="S84" s="19" t="n">
+      <x:c r="S84" s="19" t="str"/>
+      <x:c r="T84" s="19" t="str"/>
+      <x:c r="U84" s="19" t="str"/>
+      <x:c r="V84" s="19" t="str"/>
+      <x:c r="W84" s="19" t="str"/>
+      <x:c r="X84" s="19" t="str"/>
+      <x:c r="Y84" s="19" t="n">
         <x:v>83</x:v>
       </x:c>
     </x:row>
@@ -4423,7 +4951,13 @@
       <x:c r="P85" s="19" t="str"/>
       <x:c r="Q85" s="19" t="str"/>
       <x:c r="R85" s="19" t="str"/>
-      <x:c r="S85" s="19" t="n">
+      <x:c r="S85" s="19" t="str"/>
+      <x:c r="T85" s="19" t="str"/>
+      <x:c r="U85" s="19" t="str"/>
+      <x:c r="V85" s="19" t="str"/>
+      <x:c r="W85" s="19" t="str"/>
+      <x:c r="X85" s="19" t="str"/>
+      <x:c r="Y85" s="19" t="n">
         <x:v>84</x:v>
       </x:c>
     </x:row>
@@ -4462,7 +4996,13 @@
       <x:c r="P86" s="19" t="str"/>
       <x:c r="Q86" s="19" t="str"/>
       <x:c r="R86" s="19" t="str"/>
-      <x:c r="S86" s="19" t="n">
+      <x:c r="S86" s="19" t="str"/>
+      <x:c r="T86" s="19" t="str"/>
+      <x:c r="U86" s="19" t="str"/>
+      <x:c r="V86" s="19" t="str"/>
+      <x:c r="W86" s="19" t="str"/>
+      <x:c r="X86" s="19" t="str"/>
+      <x:c r="Y86" s="19" t="n">
         <x:v>85</x:v>
       </x:c>
     </x:row>
@@ -4504,7 +5044,13 @@
       <x:c r="P87" s="19" t="str"/>
       <x:c r="Q87" s="19" t="str"/>
       <x:c r="R87" s="19" t="str"/>
-      <x:c r="S87" s="19" t="n">
+      <x:c r="S87" s="19" t="str"/>
+      <x:c r="T87" s="19" t="str"/>
+      <x:c r="U87" s="19" t="str"/>
+      <x:c r="V87" s="19" t="str"/>
+      <x:c r="W87" s="19" t="str"/>
+      <x:c r="X87" s="19" t="str"/>
+      <x:c r="Y87" s="19" t="n">
         <x:v>86</x:v>
       </x:c>
     </x:row>
@@ -4541,7 +5087,13 @@
       <x:c r="P88" s="19" t="str"/>
       <x:c r="Q88" s="19" t="str"/>
       <x:c r="R88" s="19" t="str"/>
-      <x:c r="S88" s="19" t="n">
+      <x:c r="S88" s="19" t="str"/>
+      <x:c r="T88" s="19" t="str"/>
+      <x:c r="U88" s="19" t="str"/>
+      <x:c r="V88" s="19" t="str"/>
+      <x:c r="W88" s="19" t="str"/>
+      <x:c r="X88" s="19" t="str"/>
+      <x:c r="Y88" s="19" t="n">
         <x:v>87</x:v>
       </x:c>
     </x:row>
@@ -4578,7 +5130,13 @@
       <x:c r="P89" s="19" t="str"/>
       <x:c r="Q89" s="19" t="str"/>
       <x:c r="R89" s="19" t="str"/>
-      <x:c r="S89" s="19" t="n">
+      <x:c r="S89" s="19" t="str"/>
+      <x:c r="T89" s="19" t="str"/>
+      <x:c r="U89" s="19" t="str"/>
+      <x:c r="V89" s="19" t="str"/>
+      <x:c r="W89" s="19" t="str"/>
+      <x:c r="X89" s="19" t="str"/>
+      <x:c r="Y89" s="19" t="n">
         <x:v>88</x:v>
       </x:c>
     </x:row>
@@ -4615,7 +5173,13 @@
       <x:c r="P90" s="19" t="str"/>
       <x:c r="Q90" s="19" t="str"/>
       <x:c r="R90" s="19" t="str"/>
-      <x:c r="S90" s="19" t="n">
+      <x:c r="S90" s="19" t="str"/>
+      <x:c r="T90" s="19" t="str"/>
+      <x:c r="U90" s="19" t="str"/>
+      <x:c r="V90" s="19" t="str"/>
+      <x:c r="W90" s="19" t="str"/>
+      <x:c r="X90" s="19" t="str"/>
+      <x:c r="Y90" s="19" t="n">
         <x:v>89</x:v>
       </x:c>
     </x:row>
@@ -4658,7 +5222,13 @@
       <x:c r="P91" s="19" t="str"/>
       <x:c r="Q91" s="19" t="str"/>
       <x:c r="R91" s="19" t="str"/>
-      <x:c r="S91" s="19" t="n">
+      <x:c r="S91" s="19" t="str"/>
+      <x:c r="T91" s="19" t="str"/>
+      <x:c r="U91" s="19" t="str"/>
+      <x:c r="V91" s="19" t="str"/>
+      <x:c r="W91" s="19" t="str"/>
+      <x:c r="X91" s="19" t="str"/>
+      <x:c r="Y91" s="19" t="n">
         <x:v>90</x:v>
       </x:c>
     </x:row>
@@ -4703,7 +5273,13 @@
       <x:c r="P92" s="19" t="str"/>
       <x:c r="Q92" s="19" t="str"/>
       <x:c r="R92" s="19" t="str"/>
-      <x:c r="S92" s="19" t="n">
+      <x:c r="S92" s="19" t="str"/>
+      <x:c r="T92" s="19" t="str"/>
+      <x:c r="U92" s="19" t="str"/>
+      <x:c r="V92" s="19" t="str"/>
+      <x:c r="W92" s="19" t="str"/>
+      <x:c r="X92" s="19" t="str"/>
+      <x:c r="Y92" s="19" t="n">
         <x:v>91</x:v>
       </x:c>
     </x:row>
@@ -4747,7 +5323,13 @@
       <x:c r="P93" s="19" t="str"/>
       <x:c r="Q93" s="19" t="str"/>
       <x:c r="R93" s="19" t="str"/>
-      <x:c r="S93" s="19" t="n">
+      <x:c r="S93" s="19" t="str"/>
+      <x:c r="T93" s="19" t="str"/>
+      <x:c r="U93" s="19" t="str"/>
+      <x:c r="V93" s="19" t="str"/>
+      <x:c r="W93" s="19" t="str"/>
+      <x:c r="X93" s="19" t="str"/>
+      <x:c r="Y93" s="19" t="n">
         <x:v>92</x:v>
       </x:c>
     </x:row>
@@ -4784,7 +5366,13 @@
       <x:c r="P94" s="19" t="str"/>
       <x:c r="Q94" s="19" t="str"/>
       <x:c r="R94" s="19" t="str"/>
-      <x:c r="S94" s="19" t="n">
+      <x:c r="S94" s="19" t="str"/>
+      <x:c r="T94" s="19" t="str"/>
+      <x:c r="U94" s="19" t="str"/>
+      <x:c r="V94" s="19" t="str"/>
+      <x:c r="W94" s="19" t="str"/>
+      <x:c r="X94" s="19" t="str"/>
+      <x:c r="Y94" s="19" t="n">
         <x:v>93</x:v>
       </x:c>
     </x:row>
@@ -4826,7 +5414,13 @@
       <x:c r="P95" s="19" t="str"/>
       <x:c r="Q95" s="19" t="str"/>
       <x:c r="R95" s="19" t="str"/>
-      <x:c r="S95" s="19" t="n">
+      <x:c r="S95" s="19" t="str"/>
+      <x:c r="T95" s="19" t="str"/>
+      <x:c r="U95" s="19" t="str"/>
+      <x:c r="V95" s="19" t="str"/>
+      <x:c r="W95" s="19" t="str"/>
+      <x:c r="X95" s="19" t="str"/>
+      <x:c r="Y95" s="19" t="n">
         <x:v>94</x:v>
       </x:c>
     </x:row>
@@ -4871,7 +5465,13 @@
       <x:c r="P96" s="19" t="str"/>
       <x:c r="Q96" s="19" t="str"/>
       <x:c r="R96" s="19" t="str"/>
-      <x:c r="S96" s="19" t="n">
+      <x:c r="S96" s="19" t="str"/>
+      <x:c r="T96" s="19" t="str"/>
+      <x:c r="U96" s="19" t="str"/>
+      <x:c r="V96" s="19" t="str"/>
+      <x:c r="W96" s="19" t="str"/>
+      <x:c r="X96" s="19" t="str"/>
+      <x:c r="Y96" s="19" t="n">
         <x:v>95</x:v>
       </x:c>
     </x:row>
@@ -4908,7 +5508,13 @@
       <x:c r="P97" s="19" t="str"/>
       <x:c r="Q97" s="19" t="str"/>
       <x:c r="R97" s="19" t="str"/>
-      <x:c r="S97" s="19" t="n">
+      <x:c r="S97" s="19" t="str"/>
+      <x:c r="T97" s="19" t="str"/>
+      <x:c r="U97" s="19" t="str"/>
+      <x:c r="V97" s="19" t="str"/>
+      <x:c r="W97" s="19" t="str"/>
+      <x:c r="X97" s="19" t="str"/>
+      <x:c r="Y97" s="19" t="n">
         <x:v>96</x:v>
       </x:c>
     </x:row>
@@ -4945,7 +5551,13 @@
       <x:c r="P98" s="19" t="str"/>
       <x:c r="Q98" s="19" t="str"/>
       <x:c r="R98" s="19" t="str"/>
-      <x:c r="S98" s="19" t="n">
+      <x:c r="S98" s="19" t="str"/>
+      <x:c r="T98" s="19" t="str"/>
+      <x:c r="U98" s="19" t="str"/>
+      <x:c r="V98" s="19" t="str"/>
+      <x:c r="W98" s="19" t="str"/>
+      <x:c r="X98" s="19" t="str"/>
+      <x:c r="Y98" s="19" t="n">
         <x:v>97</x:v>
       </x:c>
     </x:row>
@@ -4982,7 +5594,13 @@
       <x:c r="P99" s="19" t="str"/>
       <x:c r="Q99" s="19" t="str"/>
       <x:c r="R99" s="19" t="str"/>
-      <x:c r="S99" s="19" t="n">
+      <x:c r="S99" s="19" t="str"/>
+      <x:c r="T99" s="19" t="str"/>
+      <x:c r="U99" s="19" t="str"/>
+      <x:c r="V99" s="19" t="str"/>
+      <x:c r="W99" s="19" t="str"/>
+      <x:c r="X99" s="19" t="str"/>
+      <x:c r="Y99" s="19" t="n">
         <x:v>98</x:v>
       </x:c>
     </x:row>
@@ -5024,7 +5642,13 @@
       <x:c r="P100" s="19" t="str"/>
       <x:c r="Q100" s="19" t="str"/>
       <x:c r="R100" s="19" t="str"/>
-      <x:c r="S100" s="19" t="n">
+      <x:c r="S100" s="19" t="str"/>
+      <x:c r="T100" s="19" t="str"/>
+      <x:c r="U100" s="19" t="str"/>
+      <x:c r="V100" s="19" t="str"/>
+      <x:c r="W100" s="19" t="str"/>
+      <x:c r="X100" s="19" t="str"/>
+      <x:c r="Y100" s="19" t="n">
         <x:v>99</x:v>
       </x:c>
     </x:row>
@@ -5063,12 +5687,18 @@
       <x:c r="P101" s="20" t="str"/>
       <x:c r="Q101" s="20" t="str"/>
       <x:c r="R101" s="20" t="str"/>
-      <x:c r="S101" s="20" t="n">
+      <x:c r="S101" s="20" t="str"/>
+      <x:c r="T101" s="20" t="str"/>
+      <x:c r="U101" s="20" t="str"/>
+      <x:c r="V101" s="20" t="str"/>
+      <x:c r="W101" s="20" t="str"/>
+      <x:c r="X101" s="20" t="str"/>
+      <x:c r="Y101" s="20" t="n">
         <x:v>100</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="8">
     <x:dataValidation type="list" sqref="M2:M101">
       <x:formula1>"yes,no,uncertain"</x:formula1>
     </x:dataValidation>
@@ -5079,12 +5709,24 @@
       <x:formula1>"yes,no,uncertain"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="P2:P101">
+      <x:formula1>"yes,no,uncertain"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="Q2:Q101">
+      <x:formula1>"yes,no,uncertain"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="R2:R101">
+      <x:formula1>"yes,no,uncertain"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="S2:S101">
       <x:formula1>"yes,no,uncertain,not_applicable"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="U2:U101">
+      <x:formula1>"high,medium,low"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fe604a532d0414b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd14e4182ce548cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>